--- a/event_registration_forms/049_farm_stay_reservation_form--event_registration_forms.xlsx
+++ b/event_registration_forms/049_farm_stay_reservation_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,8 +865,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -894,12 +894,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'farm_stay',_'label':_'farm_stay'}</t>
+          <t>farm_stay</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'farm_stay', 'label': 'Farm Stay'}</t>
+          <t>Farm Stay</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'glamping',_'label':_'glamping'}</t>
+          <t>glamping</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'glamping', 'label': 'Glamping'}</t>
+          <t>Glamping</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'1-1',_'label':_'1_day',_'selected':_true}</t>
+          <t>1_day</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '1-1', 'label': '1 day', 'selected': True}</t>
+          <t>1 day</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'1-2',_'label':_'2_days'}</t>
+          <t>2_days</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '1-2', 'label': '2 days'}</t>
+          <t>2 days</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'1-3',_'label':_'3_days'}</t>
+          <t>3_days</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '1-3', 'label': '3 days'}</t>
+          <t>3 days</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'1-4',_'label':_'4_days'}</t>
+          <t>4_days</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '1-4', 'label': '4 days'}</t>
+          <t>4 days</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'1-5',_'label':_'5_days'}</t>
+          <t>5_days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '1-5', 'label': '5 days'}</t>
+          <t>5 days</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'1-6',_'label':_'6_days'}</t>
+          <t>6_days</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '1-6', 'label': '6 days'}</t>
+          <t>6 days</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'cash',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'cash', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'paypal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'stripe',_'label':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 'stripe', 'label': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
